--- a/product_selector_out/STM32F1 series - diff.xlsx
+++ b/product_selector_out/STM32F1 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$283</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$235</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,6 +47,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
@@ -58,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E283"/>
+  <dimension ref="A1:E235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5865</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="18">
@@ -667,22 +667,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -694,70 +690,62 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F105VC</t>
+          <t>STM32F105VB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F105VC</t>
+          <t>STM32F105VB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -766,21 +754,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F105VC</t>
+          <t>STM32F107RB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -789,88 +777,76 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F105VB</t>
+          <t>STM32F107RB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F105VB</t>
+          <t>STM32F107RC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F105VB</t>
+          <t>STM32F107RC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F105VB</t>
+          <t>STM32F107VB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -884,7 +860,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -893,7 +869,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F105VB</t>
+          <t>STM32F107VB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -907,7 +883,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -916,102 +892,90 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F107RB</t>
+          <t>STM32F105R8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F107RB</t>
+          <t>STM32F105R8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F107RB</t>
+          <t>STM32F105RB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F107RB</t>
+          <t>STM32F105RB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1020,21 +984,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F107RB</t>
+          <t>STM32F105RC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1043,88 +1007,76 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F107RC</t>
+          <t>STM32F105RC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F107RC</t>
+          <t>STM32F105V8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F107RC</t>
+          <t>STM32F105V8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F107RC</t>
+          <t>STM32F107VC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1138,7 +1090,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1147,7 +1099,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F107RC</t>
+          <t>STM32F107VC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1161,7 +1113,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1170,229 +1122,217 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F107VB</t>
+          <t>STM32F103C4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F107VB</t>
+          <t>STM32F103C4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F107VB</t>
+          <t>STM32F103R4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>50||51</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F107VB</t>
+          <t>STM32F103R4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>50, 51</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F107VB</t>
+          <t>STM32F103R4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>50||51 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F105R8</t>
+          <t>STM32F103R4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F105R8</t>
+          <t>STM32F103R4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F105R8</t>
+          <t>STM32F103C6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F105R8</t>
+          <t>STM32F103C6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1401,21 +1341,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F105R8</t>
+          <t>STM32F103RC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1424,215 +1364,203 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F105RB</t>
+          <t>STM32F103RC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F105RB</t>
+          <t>STM32F103RE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F105RB</t>
+          <t>STM32F103RE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F105RB</t>
+          <t>STM32F103R8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>50||51</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F105RB</t>
+          <t>STM32F103R8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>50, 51</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F105RC</t>
+          <t>STM32F103R8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50||51 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F105RC</t>
+          <t>STM32F103R8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F105RC</t>
+          <t>STM32F103R8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F105RC</t>
+          <t>STM32F103RB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1646,7 +1574,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1655,7 +1583,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F105RC</t>
+          <t>STM32F103RB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1669,7 +1597,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1678,25 +1606,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F105V8</t>
+          <t>STM32F103R6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50||51</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -1705,25 +1633,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F105V8</t>
+          <t>STM32F103R6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50, 51</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -1732,25 +1660,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F105V8</t>
+          <t>STM32F103R6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>50||51 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -1759,7 +1687,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F105V8</t>
+          <t>STM32F103R6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1773,7 +1701,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1782,7 +1710,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F105V8</t>
+          <t>STM32F103R6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1796,7 +1724,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1805,102 +1733,90 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F107VC</t>
+          <t>STM32F103TB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F107VC</t>
+          <t>STM32F103TB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F107VC</t>
+          <t>STM32F103T4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F107VC</t>
+          <t>STM32F103T4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1909,21 +1825,21 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F107VC</t>
+          <t>STM32F103T8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1932,21 +1848,21 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F103C4</t>
+          <t>STM32F103T8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1955,21 +1871,21 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F103C4</t>
+          <t>STM32F103T6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1978,88 +1894,76 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F103R4</t>
+          <t>STM32F103T6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>50||51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F103R4</t>
+          <t>STM32F103CB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F103R4</t>
+          <t>STM32F103CB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>50||51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F103R4</t>
+          <t>STM32F103RF</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2073,7 +1977,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2082,7 +1986,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F103R4</t>
+          <t>STM32F103RF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2096,7 +2000,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2105,7 +2009,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F103C6</t>
+          <t>STM32F103RG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2119,7 +2023,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2128,7 +2032,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F103C6</t>
+          <t>STM32F103RG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2142,7 +2046,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2151,7 +2055,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F103RC</t>
+          <t>STM32F103VE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2165,7 +2069,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2174,7 +2078,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F103RC</t>
+          <t>STM32F103VE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2188,7 +2092,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2197,7 +2101,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F103RE</t>
+          <t>STM32F103VF</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2211,7 +2115,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2220,7 +2124,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F103RE</t>
+          <t>STM32F103VF</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2234,7 +2138,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2243,102 +2147,90 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F103R8</t>
+          <t>STM32F103VB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>50||51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F103R8</t>
+          <t>STM32F103VB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F103R8</t>
+          <t>STM32F103VG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>50||51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F103R8</t>
+          <t>STM32F103VG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2347,21 +2239,21 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F103R8</t>
+          <t>STM32F103VC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2370,21 +2262,21 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F103RB</t>
+          <t>STM32F103VC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2393,21 +2285,21 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F103RB</t>
+          <t>STM32F103ZE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2416,88 +2308,76 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F103R6</t>
+          <t>STM32F103ZE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>50||51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F103R6</t>
+          <t>STM32F103ZF</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F103R6</t>
+          <t>STM32F103ZF</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>50||51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F103R6</t>
+          <t>STM32F103ZG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2511,7 +2391,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2520,7 +2400,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F103R6</t>
+          <t>STM32F103ZG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2534,7 +2414,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2543,7 +2423,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F103TB</t>
+          <t>STM32F103V8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2557,7 +2437,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2566,7 +2446,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F103TB</t>
+          <t>STM32F103V8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2580,7 +2460,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2589,7 +2469,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F103T4</t>
+          <t>STM32F103RD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2603,7 +2483,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2612,7 +2492,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F103T4</t>
+          <t>STM32F103RD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2626,7 +2506,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2635,7 +2515,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F103T8</t>
+          <t>STM32F103ZC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2649,7 +2529,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2658,7 +2538,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F103T8</t>
+          <t>STM32F103ZC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2672,7 +2552,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2681,7 +2561,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F103T6</t>
+          <t>STM32F103ZD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2695,7 +2575,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2704,7 +2584,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F103T6</t>
+          <t>STM32F103ZD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2718,7 +2598,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2727,7 +2607,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F103CB</t>
+          <t>STM32F103C8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2741,7 +2621,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2750,7 +2630,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F103CB</t>
+          <t>STM32F103C8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2764,7 +2644,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2773,102 +2653,90 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F103VD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F103VD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F102CB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F102CB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2877,21 +2745,21 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F102R4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2900,88 +2768,76 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F102R4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F102R6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F102R6</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F102R8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2995,7 +2851,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3004,7 +2860,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F102R8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3018,7 +2874,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3027,7 +2883,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F103VE</t>
+          <t>STM32F102RB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3041,7 +2897,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3050,7 +2906,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F103VE</t>
+          <t>STM32F102RB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3064,7 +2920,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3073,102 +2929,90 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F102C4</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F102C4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F102C6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F102C6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3177,21 +3021,21 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F102C8</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3200,21 +3044,21 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F103VB</t>
+          <t>STM32F102C8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3223,21 +3067,21 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F103VB</t>
+          <t>STM32F100VC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3246,88 +3090,76 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F100VC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F100CB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F100CB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F100VD</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3341,7 +3173,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3350,7 +3182,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F100VD</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3364,7 +3196,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3373,7 +3205,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32F103VC</t>
+          <t>STM32F100R4</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3387,7 +3219,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3396,7 +3228,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32F103VC</t>
+          <t>STM32F100R4</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3410,7 +3242,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3419,7 +3251,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32F103ZE</t>
+          <t>STM32F100VE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3433,7 +3265,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3442,7 +3274,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32F103ZE</t>
+          <t>STM32F100VE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3456,7 +3288,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3465,102 +3297,90 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F100R6</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F100R6</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F100R8</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F100R8</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3569,21 +3389,21 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F100RB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3592,88 +3412,76 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32F103ZG</t>
+          <t>STM32F100RB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32F103ZG</t>
+          <t>STM32F100RC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32F103ZG</t>
+          <t>STM32F100RC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32F103ZG</t>
+          <t>STM32F100RD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3687,7 +3495,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3696,7 +3504,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32F103ZG</t>
+          <t>STM32F100RD</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3710,7 +3518,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3719,7 +3527,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32F103V8</t>
+          <t>STM32F100RE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3733,7 +3541,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3742,7 +3550,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32F103V8</t>
+          <t>STM32F100RE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3756,7 +3564,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3765,7 +3573,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32F103RD</t>
+          <t>STM32F100V8</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3779,7 +3587,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3788,7 +3596,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32F103RD</t>
+          <t>STM32F100V8</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3802,7 +3610,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3811,7 +3619,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32F103ZC</t>
+          <t>STM32F100C4</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3825,7 +3633,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3834,7 +3642,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32F103ZC</t>
+          <t>STM32F100C4</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3848,7 +3656,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3857,7 +3665,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32F103ZD</t>
+          <t>STM32F100VB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3871,7 +3679,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3880,7 +3688,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32F103ZD</t>
+          <t>STM32F100VB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3894,7 +3702,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3903,7 +3711,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32F103C8</t>
+          <t>STM32F100C6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3917,7 +3725,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3926,7 +3734,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32F103C8</t>
+          <t>STM32F100C6</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3940,7 +3748,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3949,7 +3757,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32F103VD</t>
+          <t>STM32F100C8</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3963,7 +3771,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3972,7 +3780,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32F103VD</t>
+          <t>STM32F100C8</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3986,7 +3794,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -3995,7 +3803,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32F102CB</t>
+          <t>STM32F100ZE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4009,7 +3817,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4018,7 +3826,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32F102CB</t>
+          <t>STM32F100ZE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4032,7 +3840,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4041,7 +3849,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32F102R4</t>
+          <t>STM32F100ZC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4055,7 +3863,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4064,7 +3872,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32F102R4</t>
+          <t>STM32F100ZC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4078,7 +3886,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4087,7 +3895,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32F102R6</t>
+          <t>STM32F100ZD</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4101,7 +3909,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4110,7 +3918,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32F102R6</t>
+          <t>STM32F100ZD</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4124,7 +3932,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4133,7 +3941,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32F102R8</t>
+          <t>STM32F101T4</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4147,7 +3955,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4156,7 +3964,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32F102R8</t>
+          <t>STM32F101T4</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4170,7 +3978,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4179,90 +3987,102 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32F102RB</t>
+          <t>STM32F101VG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32F102RB</t>
+          <t>STM32F101VG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32F102C4</t>
+          <t>STM32F101VG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32F102C4</t>
+          <t>STM32F101VG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4271,21 +4091,21 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32F102C6</t>
+          <t>STM32F101VG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E166" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4294,76 +4114,88 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32F102C6</t>
+          <t>STM32F101ZF</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E167" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32F102C8</t>
+          <t>STM32F101ZF</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32F102C8</t>
+          <t>STM32F101ZF</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32F100VC</t>
+          <t>STM32F101ZF</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4377,7 +4209,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4386,7 +4218,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32F100VC</t>
+          <t>STM32F101ZF</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4400,7 +4232,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4409,90 +4241,102 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32F100CB</t>
+          <t>STM32F101ZG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32F100CB</t>
+          <t>STM32F101ZG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32F100VD</t>
+          <t>STM32F101ZG</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32F100VD</t>
+          <t>STM32F101ZG</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4501,21 +4345,21 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32F100R4</t>
+          <t>STM32F101ZG</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4524,76 +4368,88 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32F100R4</t>
+          <t>STM32F101RF</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32F100VE</t>
+          <t>STM32F101RF</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32F100VE</t>
+          <t>STM32F101RF</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32F100R6</t>
+          <t>STM32F101RF</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4607,7 +4463,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4616,7 +4472,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32F100R6</t>
+          <t>STM32F101RF</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4630,7 +4486,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4639,90 +4495,102 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32F100R8</t>
+          <t>STM32F101RG</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32F100R8</t>
+          <t>STM32F101RG</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E183" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32F100RB</t>
+          <t>STM32F101RG</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32F100RB</t>
+          <t>STM32F101RG</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E185" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4731,21 +4599,21 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32F100RC</t>
+          <t>STM32F101RG</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4754,21 +4622,21 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32F100RC</t>
+          <t>STM32F101C4</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E187" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4777,21 +4645,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32F100RD</t>
+          <t>STM32F101C4</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E188" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4800,76 +4668,88 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32F100RD</t>
+          <t>STM32F101VF</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E189" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32F100RE</t>
+          <t>STM32F101VF</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E190" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32F100RE</t>
+          <t>STM32F101VF</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32F100V8</t>
+          <t>STM32F101VF</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4883,7 +4763,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4892,7 +4772,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32F100V8</t>
+          <t>STM32F101VF</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4906,7 +4786,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4915,7 +4795,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32F100C4</t>
+          <t>STM32F101C6</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4929,7 +4809,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4938,7 +4818,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32F100C4</t>
+          <t>STM32F101C6</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4952,7 +4832,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4961,7 +4841,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32F100VB</t>
+          <t>STM32F101C8</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4975,7 +4855,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -4984,7 +4864,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32F100VB</t>
+          <t>STM32F101C8</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4998,7 +4878,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5007,7 +4887,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32F100C6</t>
+          <t>STM32F101R6</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5021,7 +4901,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5030,7 +4910,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32F100C6</t>
+          <t>STM32F101R6</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5044,7 +4924,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5053,7 +4933,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32F100C8</t>
+          <t>STM32F101R8</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5067,7 +4947,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5076,7 +4956,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32F100C8</t>
+          <t>STM32F101R8</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5090,7 +4970,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5099,7 +4979,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32F100ZE</t>
+          <t>STM32F101TB</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5113,7 +4993,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5122,7 +5002,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32F100ZE</t>
+          <t>STM32F101TB</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5136,7 +5016,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5145,7 +5025,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32F100ZC</t>
+          <t>STM32F101VC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5159,7 +5039,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5168,7 +5048,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32F100ZC</t>
+          <t>STM32F101VC</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5182,7 +5062,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5191,7 +5071,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32F100ZD</t>
+          <t>STM32F101VE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5205,7 +5085,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5214,7 +5094,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32F100ZD</t>
+          <t>STM32F101VE</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5228,7 +5108,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5237,7 +5117,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32F101T4</t>
+          <t>STM32F101V8</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5251,7 +5131,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5260,7 +5140,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32F101T4</t>
+          <t>STM32F101V8</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5274,7 +5154,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5283,102 +5163,90 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32F101VG</t>
+          <t>STM32F101VB</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32F101VG</t>
+          <t>STM32F101VB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E211" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32F101VG</t>
+          <t>STM32F101ZC</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32F101VG</t>
+          <t>STM32F101ZC</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E213" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5387,21 +5255,21 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32F101VG</t>
+          <t>STM32F101ZE</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E214" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5410,88 +5278,76 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32F101ZF</t>
+          <t>STM32F101ZE</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32F101ZF</t>
+          <t>STM32F101T8</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32F101ZF</t>
+          <t>STM32F101T8</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E217" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32F101ZF</t>
+          <t>STM32F101T6</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5505,7 +5361,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5514,7 +5370,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32F101ZF</t>
+          <t>STM32F101T6</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5528,7 +5384,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5537,102 +5393,90 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32F101ZG</t>
+          <t>STM32F101R4</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32F101ZG</t>
+          <t>STM32F101R4</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32F101ZG</t>
+          <t>STM32F101VD</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E222" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32F101ZG</t>
+          <t>STM32F101VD</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E223" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5641,21 +5485,21 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32F101ZG</t>
+          <t>STM32F101ZD</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E224" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5664,88 +5508,76 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32F101RF</t>
+          <t>STM32F101ZD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32F101RF</t>
+          <t>STM32F101RE</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32F101RF</t>
+          <t>STM32F101RE</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E227" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32F101RF</t>
+          <t>STM32F101RD</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5759,7 +5591,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E228" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5768,7 +5600,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STM32F101RF</t>
+          <t>STM32F101RD</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5782,7 +5614,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5791,102 +5623,90 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32F101RG</t>
+          <t>STM32F101CB</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32F101RG</t>
+          <t>STM32F101CB</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E231" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32F101RG</t>
+          <t>STM32F101RB</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E232" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32F101RG</t>
+          <t>STM32F101RB</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E233" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5895,21 +5715,21 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32F101RG</t>
+          <t>STM32F101RC</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E234" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -5918,1144 +5738,28 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32F101C4</t>
+          <t>STM32F101RC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E235" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>STM32F101C4</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E236" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>STM32F101VF</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>STM32F101VF</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E238" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>STM32F101VF</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E239" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>STM32F101VF</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E240" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>STM32F101VF</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E241" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>STM32F101C6</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E242" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>STM32F101C6</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E243" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>STM32F101C8</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E244" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>STM32F101C8</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E245" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>STM32F101R6</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E246" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>STM32F101R6</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E247" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>STM32F101R8</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E248" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>STM32F101R8</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E249" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>STM32F101TB</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E250" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>STM32F101TB</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E251" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>STM32F101VC</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E252" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>STM32F101VC</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E253" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>STM32F101VE</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E254" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>STM32F101VE</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E255" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>STM32F101V8</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E256" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>STM32F101V8</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E257" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>STM32F101VB</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E258" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>STM32F101VB</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E259" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>STM32F101ZC</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E260" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>STM32F101ZC</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E261" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>STM32F101ZE</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E262" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>STM32F101ZE</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E263" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>STM32F101T8</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E264" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>STM32F101T8</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E265" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>STM32F101T6</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E266" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>STM32F101T6</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E267" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>STM32F101R4</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E268" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>STM32F101R4</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E269" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>STM32F101VD</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E270" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>STM32F101VD</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E271" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>STM32F101ZD</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E272" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>STM32F101ZD</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E273" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>STM32F101RE</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E274" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>STM32F101RE</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E275" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>STM32F101RD</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E276" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>STM32F101RD</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E277" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>STM32F101CB</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr"/>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E278" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>STM32F101CB</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E279" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>STM32F101RB</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr"/>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E280" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>STM32F101RB</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr"/>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E281" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>STM32F101RC</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E282" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>STM32F101RC</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E283" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E283"/>
+  <autoFilter ref="A18:E235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F1 series - diff.xlsx
+++ b/product_selector_out/STM32F1 series - diff.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6080</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5881</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="18">
